--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -1701,7 +1701,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Juånäset</t>
+          <t>Floarna</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>94.90000000000001</v>
+        <v>724.7</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>22</v>
+      </c>
+      <c r="M9" t="n">
         <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1750,18 +1750,154 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>36</v>
+      </c>
+      <c r="T9" t="n">
+        <v>139</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>Urskogsporing
+Doftticka
+Fläckporing
+Garnlav
+Gräddporing
+Knärot
+Rotfingersvamp
+Skrovlig taggsvamp
+Blanksvart spiklav
+Blågrå svartspik
+Doftskinn
+Dropptaggsvamp
+Dvärgbägarlav
+Kolflarnlav
+Kortskaftad ärgspik
+Lunglav
+Mörk kolflarnlav
+Nordtagging
+Orange taggsvamp
+Reliktbock
+Rynkskinn
+Stiftgelélav
+Tallticka
+Ullticka
+Vaddporing
+Vedflamlav
+Vedskivlav
+Vedtrappmossa
+Vitplätt
+Äggvaxskivling
+Gräsull
+Nästlav
+Trådticka
+Järpe
+Smålom
+Utter</t>
+        </is>
+      </c>
+      <c r="V9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Floarna artfynd.xlsx", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Floarna karta.png", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Floarna karta knärot.png", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Floarna FSC-klagomål.docx", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Floarna FSC-klagomål mail.docx", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Floarna tillsynsbegäran.docx", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Floarna tillsynsbegäran mail.docx", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Floarna prioriterade fågelarter.docx", "Floarna")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juånäset</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>18</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>34</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>109</v>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>Storspov
 Garnlav
@@ -1799,103 +1935,103 @@
 Trana</t>
         </is>
       </c>
-      <c r="V9">
+      <c r="V10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Juånäset artfynd.xlsx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Juånäset karta.png", "Juånäset")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Juånäset karta knärot.png", "Juånäset")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Juånäset FSC-klagomål.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Juånäset FSC-klagomål mail.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Juånäset tillsynsbegäran.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Juånäset tillsynsbegäran mail.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Juånäset prioriterade fågelarter.docx", "Juånäset")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D11" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>751.8</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>7</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>20</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>26</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>6</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>34</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>240</v>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Fläckporing
@@ -1933,172 +2069,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V10">
+      <c r="V11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Fröbäckstjärnarna artfynd.xlsx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Fröbäckstjärnarna karta.png", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Fröbäckstjärnarna karta knärot.png", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Fröbäckstjärnarna FSC-klagomål.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Fröbäckstjärnarna FSC-klagomål mail.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Fröbäckstjärnarna tillsynsbegäran.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Fröbäckstjärnarna tillsynsbegäran mail.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Fröbäckstjärnarna prioriterade fågelarter.docx", "Fröbäckstjärnarna")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Floarna</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Jämtlands län</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>724.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>17</v>
-      </c>
-      <c r="M11" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>25</v>
-      </c>
-      <c r="R11" t="n">
-        <v>8</v>
-      </c>
-      <c r="S11" t="n">
-        <v>29</v>
-      </c>
-      <c r="T11" t="n">
-        <v>99</v>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>Urskogsporing
-Doftticka
-Fläckporing
-Garnlav
-Gräddporing
-Knärot
-Rotfingersvamp
-Skrovlig taggsvamp
-Doftskinn
-Dropptaggsvamp
-Dvärgbägarlav
-Kortskaftad ärgspik
-Lunglav
-Mörk kolflarnlav
-Nordtagging
-Orange taggsvamp
-Reliktbock
-Rynkskinn
-Stiftgelélav
-Tallticka
-Vaddporing
-Vedflamlav
-Vedtrappmossa
-Vitplätt
-Äggvaxskivling
-Trådticka
-Järpe
-Smålom
-Utter</t>
-        </is>
-      </c>
-      <c r="V11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Floarna artfynd.xlsx", "Floarna")</f>
-        <v/>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Floarna karta.png", "Floarna")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Floarna karta knärot.png", "Floarna")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Floarna FSC-klagomål.docx", "Floarna")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Floarna FSC-klagomål mail.docx", "Floarna")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Floarna tillsynsbegäran.docx", "Floarna")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Floarna tillsynsbegäran mail.docx", "Floarna")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Floarna prioriterade fågelarter.docx", "Floarna")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Holmnäset</t>
+          <t>Bodsjön</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2123,22 +2130,22 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>163.9</v>
+        <v>49.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2147,18 +2154,143 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
       </c>
       <c r="T12" t="n">
+        <v>90</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Gammelgransskål
+Lunglav
+Mörk kolflarnlav
+Rosenticka
+Rynkskinn
+Skrovellav
+Stiftgelélav
+Talltita
+Tretåig hackspett
+Ullticka
+Vitgrynig nållav
+Bollvitmossa
+Bårdlav
+Korallblylav
+Luddlav
+Stuplav
+Trådticka
+Vedticka
+Kransmossa
+Spillkråka
+Timmerticka
+Torta
+Revlummer</t>
+        </is>
+      </c>
+      <c r="V12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Bodsjön artfynd.xlsx", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Bodsjön karta.png", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Bodsjön karta knärot.png", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Bodsjön FSC-klagomål.docx", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Bodsjön FSC-klagomål mail.docx", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Bodsjön tillsynsbegäran.docx", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Bodsjön tillsynsbegäran mail.docx", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Bodsjön prioriterade fågelarter.docx", "Bodsjön")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Holmnäset</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="n">
         <v>141</v>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Fläckporing
@@ -2187,99 +2319,99 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V12">
+      <c r="V13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Holmnäset artfynd.xlsx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Holmnäset karta.png", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Holmnäset karta knärot.png", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Holmnäset FSC-klagomål.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Holmnäset FSC-klagomål mail.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Holmnäset tillsynsbegäran.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Holmnäset tillsynsbegäran mail.docx", "Holmnäset")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Staverberget SCA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="D14" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>115.3</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>13</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>4</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>17</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>4</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>23</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>82</v>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -2306,103 +2438,103 @@
 Orre</t>
         </is>
       </c>
-      <c r="V13">
+      <c r="V14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Staverberget SCA artfynd.xlsx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Staverberget SCA karta.png", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Staverberget SCA karta knärot.png", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Staverberget SCA FSC-klagomål.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Staverberget SCA FSC-klagomål mail.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Staverberget SCA tillsynsbegäran.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Staverberget SCA tillsynsbegäran mail.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Staverberget SCA prioriterade fågelarter.docx", "Staverberget SCA")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Björnbäcken</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D15" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>61.4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>12</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>15</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>23</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>74</v>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -2429,103 +2561,103 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V14">
+      <c r="V15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Björnbäcken artfynd.xlsx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Björnbäcken karta.png", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Björnbäcken karta knärot.png", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Björnbäcken FSC-klagomål.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Björnbäcken FSC-klagomål mail.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Björnbäcken tillsynsbegäran.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Björnbäcken tillsynsbegäran mail.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Björnbäcken prioriterade fågelarter.docx", "Björnbäcken")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Kilkojan</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D16" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>162.6</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>15</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>4</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>19</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>4</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>19</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>56</v>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Fläckporing
@@ -2548,99 +2680,99 @@
 Vitplätt</t>
         </is>
       </c>
-      <c r="V15">
+      <c r="V16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Kilkojan artfynd.xlsx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Kilkojan karta.png", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Kilkojan FSC-klagomål.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Kilkojan FSC-klagomål mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Kilkojan tillsynsbegäran.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Kilkojan tillsynsbegäran mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kilkojan prioriterade fågelarter.docx", "Kilkojan")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Börsåsen N</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D17" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>124.6</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" t="n">
         <v>8</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>6</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>3</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>9</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>18</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>60</v>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Garnlav
@@ -2662,99 +2794,99 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="V16">
+      <c r="V17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Börsåsen N artfynd.xlsx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Börsåsen N karta.png", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Börsåsen N karta knärot.png", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Börsåsen N FSC-klagomål.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Börsåsen N FSC-klagomål mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Börsåsen N tillsynsbegäran.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Börsåsen N tillsynsbegäran mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Kölavallhöjden</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="D18" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>57.8</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>10</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>16</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>36</v>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Knärot
@@ -2774,103 +2906,103 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="V17">
+      <c r="V18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Kölavallhöjden artfynd.xlsx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Kölavallhöjden karta.png", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Kölavallhöjden karta knärot.png", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Kölavallhöjden FSC-klagomål.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Kölavallhöjden FSC-klagomål mail.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Kölavallhöjden tillsynsbegäran.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Kölavallhöjden tillsynsbegäran mail.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kölavallhöjden prioriterade fågelarter.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Trollkärringberget</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D19" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>18.8</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>6</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>3</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>9</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>3</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>16</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>39</v>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2890,99 +3022,99 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="V18">
+      <c r="V19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Trollkärringberget artfynd.xlsx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Trollkärringberget karta.png", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Trollkärringberget karta knärot.png", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Trollkärringberget FSC-klagomål.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Trollkärringberget FSC-klagomål mail.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Trollkärringberget tillsynsbegäran.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Trollkärringberget tillsynsbegäran mail.docx", "Trollkärringberget")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Nils-Andersknulen N</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D20" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>45.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L20" t="n">
         <v>6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M20" t="n">
         <v>2</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>8</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
         <v>11</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>12</v>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>Blackticka
 Gränsticka
@@ -2997,138 +3129,32 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V19">
+      <c r="V20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Nils-Andersknulen N artfynd.xlsx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Nils-Andersknulen N karta.png", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Nils-Andersknulen N FSC-klagomål.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Nils-Andersknulen N FSC-klagomål mail.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Nils-Andersknulen N tillsynsbegäran.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Nils-Andersknulen N tillsynsbegäran mail.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Nils-Andersknulen N prioriterade fågelarter.docx", "Nils-Andersknulen N")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Bodsjön</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Jämtlands län</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>15</v>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Gammelgransskål
-Lunglav
-Skrovellav
-Stiftgelélav
-Vitgrynig nållav
-Bollvitmossa
-Korallblylav
-Luddlav
-Stuplav</t>
-        </is>
-      </c>
-      <c r="V20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Bodsjön artfynd.xlsx", "Bodsjön")</f>
-        <v/>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Bodsjön karta.png", "Bodsjön")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Bodsjön karta knärot.png", "Bodsjön")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Bodsjön FSC-klagomål.docx", "Bodsjön")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Bodsjön FSC-klagomål mail.docx", "Bodsjön")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Bodsjön tillsynsbegäran.docx", "Bodsjön")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Bodsjön tillsynsbegäran mail.docx", "Bodsjön")</f>
         <v/>
       </c>
     </row>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -2597,67 +2597,184 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Börsåsen N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" t="n">
+        <v>63</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Doftticka
+Garnlav
+Knärot
+Blanksvart spiklav
+Dropptaggsvamp
+Lunglav
+Mörk kolflarnlav
+Rynkskinn
+Skrovellav
+Ullticka
+Vedflamlav
+Vedskivlav
+Bårdlav
+Korallblylav
+Kransrams
+Norrlandslav
+Spindelblomster
+Stor aspticka
+Stuplav
+Ögonpyrola
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="V16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Börsåsen N artfynd.xlsx", "Börsåsen N")</f>
+        <v/>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Börsåsen N karta.png", "Börsåsen N")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Börsåsen N karta knärot.png", "Börsåsen N")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Börsåsen N FSC-klagomål.docx", "Börsåsen N")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Börsåsen N FSC-klagomål mail.docx", "Börsåsen N")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Börsåsen N tillsynsbegäran.docx", "Börsåsen N")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Börsåsen N tillsynsbegäran mail.docx", "Börsåsen N")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Kilkojan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D17" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>162.6</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>15</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>4</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>19</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>19</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>56</v>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Fläckporing
@@ -2680,146 +2797,32 @@
 Vitplätt</t>
         </is>
       </c>
-      <c r="V16">
+      <c r="V17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Kilkojan artfynd.xlsx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Kilkojan karta.png", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Kilkojan FSC-klagomål.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Kilkojan FSC-klagomål mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Kilkojan tillsynsbegäran.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Kilkojan tillsynsbegäran mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kilkojan prioriterade fågelarter.docx", "Kilkojan")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Börsåsen N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Jämtlands län</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>124.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>60</v>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>Doftticka
-Garnlav
-Knärot
-Lunglav
-Mörk kolflarnlav
-Rynkskinn
-Skrovellav
-Ullticka
-Vedskivlav
-Bårdlav
-Korallblylav
-Kransrams
-Norrlandslav
-Spindelblomster
-Stor aspticka
-Stuplav
-Ögonpyrola
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="V17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Börsåsen N artfynd.xlsx", "Börsåsen N")</f>
-        <v/>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Börsåsen N karta.png", "Börsåsen N")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Börsåsen N karta knärot.png", "Börsåsen N")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Börsåsen N FSC-klagomål.docx", "Börsåsen N")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Börsåsen N FSC-klagomål mail.docx", "Börsåsen N")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Börsåsen N tillsynsbegäran.docx", "Börsåsen N")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Börsåsen N tillsynsbegäran mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
     </row>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -542,30 +542,35 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Geotifflänk</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -744,26 +749,30 @@
         <v/>
       </c>
       <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Tokberget georefererad karta.tif", "Tokberget")</f>
+        <v/>
+      </c>
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Tokberget karta knärot.png", "Tokberget")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Tokberget FSC-klagomål.docx", "Tokberget")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Tokberget FSC-klagomål mail.docx", "Tokberget")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Tokberget tillsynsbegäran.docx", "Tokberget")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Tokberget tillsynsbegäran mail.docx", "Tokberget")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Tokberget prioriterade fågelarter.docx", "Tokberget")</f>
         <v/>
       </c>
@@ -928,26 +937,30 @@
         <v/>
       </c>
       <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Örasjöberget georefererad karta.tif", "Örasjöberget")</f>
+        <v/>
+      </c>
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Örasjöberget karta knärot.png", "Örasjöberget")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Örasjöberget FSC-klagomål.docx", "Örasjöberget")</f>
         <v/>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Örasjöberget FSC-klagomål mail.docx", "Örasjöberget")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Örasjöberget tillsynsbegäran.docx", "Örasjöberget")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Örasjöberget tillsynsbegäran mail.docx", "Örasjöberget")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Örasjöberget prioriterade fågelarter.docx", "Örasjöberget")</f>
         <v/>
       </c>
@@ -1094,26 +1107,30 @@
         <v/>
       </c>
       <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Halstjärnarna georefererad karta.tif", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Halstjärnarna karta knärot.png", "Halstjärnarna")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Halstjärnarna FSC-klagomål.docx", "Halstjärnarna")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Halstjärnarna FSC-klagomål mail.docx", "Halstjärnarna")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Halstjärnarna tillsynsbegäran.docx", "Halstjärnarna")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Halstjärnarna tillsynsbegäran mail.docx", "Halstjärnarna")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Halstjärnarna prioriterade fågelarter.docx", "Halstjärnarna")</f>
         <v/>
       </c>
@@ -1257,26 +1274,30 @@
         <v/>
       </c>
       <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Horten Sultentjärnen georefererad karta.tif", "Horten Sultentjärnen")</f>
+        <v/>
+      </c>
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Horten Sultentjärnen karta knärot.png", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Horten Sultentjärnen FSC-klagomål.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Horten Sultentjärnen FSC-klagomål mail.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Horten Sultentjärnen tillsynsbegäran.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Horten Sultentjärnen tillsynsbegäran mail.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Horten Sultentjärnen prioriterade fågelarter.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
@@ -1402,26 +1423,30 @@
         <v/>
       </c>
       <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Hundtjärnbrännan georefererad karta.tif", "Hundtjärnbrännan")</f>
+        <v/>
+      </c>
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Hundtjärnbrännan karta knärot.png", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Hundtjärnbrännan FSC-klagomål.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Hundtjärnbrännan FSC-klagomål mail.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Hundtjärnbrännan tillsynsbegäran.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Hundtjärnbrännan tillsynsbegäran mail.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Hundtjärnbrännan prioriterade fågelarter.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
@@ -1543,26 +1568,30 @@
         <v/>
       </c>
       <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Länken Vitalmen georefererad karta.tif", "Länken Vitalmen")</f>
+        <v/>
+      </c>
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Länken Vitalmen karta knärot.png", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Länken Vitalmen FSC-klagomål.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Länken Vitalmen FSC-klagomål mail.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Länken Vitalmen tillsynsbegäran.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Länken Vitalmen tillsynsbegäran mail.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Länken Vitalmen prioriterade fågelarter.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
@@ -1681,19 +1710,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Gräsmyren karta.png", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Gräsmyren georefererad karta.tif", "Gräsmyren")</f>
+        <v/>
+      </c>
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Gräsmyren FSC-klagomål.docx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Gräsmyren FSC-klagomål mail.docx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Gräsmyren tillsynsbegäran.docx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Gräsmyren tillsynsbegäran mail.docx", "Gräsmyren")</f>
         <v/>
       </c>
@@ -1810,26 +1843,30 @@
         <v/>
       </c>
       <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Floarna georefererad karta.tif", "Floarna")</f>
+        <v/>
+      </c>
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Floarna karta knärot.png", "Floarna")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Floarna FSC-klagomål.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Floarna FSC-klagomål mail.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Floarna tillsynsbegäran.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Floarna tillsynsbegäran mail.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Floarna prioriterade fågelarter.docx", "Floarna")</f>
         <v/>
       </c>
@@ -1944,26 +1981,30 @@
         <v/>
       </c>
       <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Juånäset georefererad karta.tif", "Juånäset")</f>
+        <v/>
+      </c>
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Juånäset karta knärot.png", "Juånäset")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Juånäset FSC-klagomål.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Juånäset FSC-klagomål mail.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Juånäset tillsynsbegäran.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Juånäset tillsynsbegäran mail.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Juånäset prioriterade fågelarter.docx", "Juånäset")</f>
         <v/>
       </c>
@@ -2078,26 +2119,30 @@
         <v/>
       </c>
       <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Fröbäckstjärnarna georefererad karta.tif", "Fröbäckstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Fröbäckstjärnarna karta knärot.png", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Fröbäckstjärnarna FSC-klagomål.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Fröbäckstjärnarna FSC-klagomål mail.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Fröbäckstjärnarna tillsynsbegäran.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Fröbäckstjärnarna tillsynsbegäran mail.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Fröbäckstjärnarna prioriterade fågelarter.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
@@ -2203,26 +2248,30 @@
         <v/>
       </c>
       <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Bodsjön georefererad karta.tif", "Bodsjön")</f>
+        <v/>
+      </c>
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Bodsjön karta knärot.png", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Bodsjön FSC-klagomål.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Bodsjön FSC-klagomål mail.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Bodsjön tillsynsbegäran.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Bodsjön tillsynsbegäran mail.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Bodsjön prioriterade fågelarter.docx", "Bodsjön")</f>
         <v/>
       </c>
@@ -2328,22 +2377,26 @@
         <v/>
       </c>
       <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Holmnäset georefererad karta.tif", "Holmnäset")</f>
+        <v/>
+      </c>
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Holmnäset karta knärot.png", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Holmnäset FSC-klagomål.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Holmnäset FSC-klagomål mail.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Holmnäset tillsynsbegäran.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Holmnäset tillsynsbegäran mail.docx", "Holmnäset")</f>
         <v/>
       </c>
@@ -2447,26 +2500,30 @@
         <v/>
       </c>
       <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Staverberget SCA georefererad karta.tif", "Staverberget SCA")</f>
+        <v/>
+      </c>
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Staverberget SCA karta knärot.png", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Staverberget SCA FSC-klagomål.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Staverberget SCA FSC-klagomål mail.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Staverberget SCA tillsynsbegäran.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Staverberget SCA tillsynsbegäran mail.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Staverberget SCA prioriterade fågelarter.docx", "Staverberget SCA")</f>
         <v/>
       </c>
@@ -2570,26 +2627,30 @@
         <v/>
       </c>
       <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Björnbäcken georefererad karta.tif", "Björnbäcken")</f>
+        <v/>
+      </c>
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Björnbäcken karta knärot.png", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Björnbäcken FSC-klagomål.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Björnbäcken FSC-klagomål mail.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Björnbäcken tillsynsbegäran.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Björnbäcken tillsynsbegäran mail.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Björnbäcken prioriterade fågelarter.docx", "Björnbäcken")</f>
         <v/>
       </c>
@@ -2691,22 +2752,26 @@
         <v/>
       </c>
       <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Börsåsen N georefererad karta.tif", "Börsåsen N")</f>
+        <v/>
+      </c>
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Börsåsen N karta knärot.png", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Börsåsen N FSC-klagomål.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Börsåsen N FSC-klagomål mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Börsåsen N tillsynsbegäran.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Börsåsen N tillsynsbegäran mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
@@ -2805,23 +2870,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Kilkojan karta.png", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Kilkojan georefererad karta.tif", "Kilkojan")</f>
+        <v/>
+      </c>
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Kilkojan FSC-klagomål.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Kilkojan FSC-klagomål mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Kilkojan tillsynsbegäran.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Kilkojan tillsynsbegäran mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kilkojan prioriterade fågelarter.docx", "Kilkojan")</f>
         <v/>
       </c>
@@ -2918,26 +2987,30 @@
         <v/>
       </c>
       <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Kölavallhöjden georefererad karta.tif", "Kölavallhöjden")</f>
+        <v/>
+      </c>
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Kölavallhöjden karta knärot.png", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Kölavallhöjden FSC-klagomål.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Kölavallhöjden FSC-klagomål mail.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Kölavallhöjden tillsynsbegäran.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Kölavallhöjden tillsynsbegäran mail.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kölavallhöjden prioriterade fågelarter.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
@@ -3034,22 +3107,26 @@
         <v/>
       </c>
       <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Trollkärringberget georefererad karta.tif", "Trollkärringberget")</f>
+        <v/>
+      </c>
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Trollkärringberget karta knärot.png", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Trollkärringberget FSC-klagomål.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Trollkärringberget FSC-klagomål mail.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Trollkärringberget tillsynsbegäran.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Trollkärringberget tillsynsbegäran mail.docx", "Trollkärringberget")</f>
         <v/>
       </c>
@@ -3140,23 +3217,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Nils-Andersknulen N karta.png", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Nils-Andersknulen N georefererad karta.tif", "Nils-Andersknulen N")</f>
+        <v/>
+      </c>
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Nils-Andersknulen N FSC-klagomål.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Nils-Andersknulen N FSC-klagomål mail.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Nils-Andersknulen N tillsynsbegäran.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Nils-Andersknulen N tillsynsbegäran mail.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Nils-Andersknulen N prioriterade fågelarter.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
@@ -3245,26 +3326,30 @@
         <v/>
       </c>
       <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Blåtjärnen georefererad karta.tif", "Blåtjärnen")</f>
+        <v/>
+      </c>
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Blåtjärnen karta knärot.png", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Blåtjärnen FSC-klagomål.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Blåtjärnen FSC-klagomål mail.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Blåtjärnen tillsynsbegäran.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Blåtjärnen tillsynsbegäran mail.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Blåtjärnen prioriterade fågelarter.docx", "Blåtjärnen")</f>
         <v/>
       </c>
@@ -3351,19 +3436,23 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Sjättnäsbäcken SCA karta.png", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Sjättnäsbäcken SCA georefererad karta.tif", "Sjättnäsbäcken SCA")</f>
+        <v/>
+      </c>
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Sjättnäsbäcken SCA FSC-klagomål.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Sjättnäsbäcken SCA FSC-klagomål mail.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Sjättnäsbäcken SCA tillsynsbegäran.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Sjättnäsbäcken SCA tillsynsbegäran mail.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
@@ -3450,22 +3539,26 @@
         <v/>
       </c>
       <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Rammsjöberget V Sveaskog georefererad karta.tif", "Rammsjöberget V Sveaskog")</f>
+        <v/>
+      </c>
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Rammsjöberget V Sveaskog karta knärot.png", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Rammsjöberget V Sveaskog FSC-klagomål.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Rammsjöberget V Sveaskog FSC-klagomål mail.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Rammsjöberget V Sveaskog tillsynsbegäran.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Rammsjöberget V Sveaskog tillsynsbegäran mail.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -573,6 +573,46 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Ägare</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Avv</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Avsatt</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Påverkan</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Granskad</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Prio</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Typ</t>
         </is>
       </c>
     </row>
@@ -776,6 +816,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Tokberget prioriterade fågelarter.docx", "Tokberget")</f>
         <v/>
       </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Kyrkan + SCA</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Endast lite i N</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>LST Jämtland positiva till inv av detta område</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Troligen ganska låg</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -964,6 +1040,45 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Örasjöberget prioriterade fågelarter.docx", "Örasjöberget")</f>
         <v/>
       </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Stora avv i V och S</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Ställvis gallrat, men troligtvis åtminstone delar fin stava</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Måttlig</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Örasjöberget sydligaste området
+Genomgallrad tallnaturskog
+fler artfynd, bör inventeras
+Gammeltallar och silverved</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -1134,6 +1249,40 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Halstjärnarna prioriterade fågelarter.docx", "Halstjärnarna")</f>
         <v/>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Ser bra ut</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Stor påverkan centralt, annars ganska låg</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -1301,6 +1450,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Horten Sultentjärnen prioriterade fågelarter.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Flera stora avv</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ser riktigt bra ut!</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -1450,6 +1635,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Hundtjärnbrännan prioriterade fågelarter.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Stor avv i O</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Mycket lovande, gränsar till två reservat</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Troligen medelpåverkan</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Lst Vst: Har rätt bra koll på detta omr</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1595,6 +1816,45 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Länken Vitalmen prioriterade fågelarter.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>SCA + kyrkan</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Flera avv</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Liten del av omr</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ser tätt och bra ut</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>I s: Stavatall, 80-100, inga överståndare. Gallrad en gång länge sedan. Sparsamt med död ved.
+I N klockrent. U/V3</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1730,6 +1990,40 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Gräsmyren tillsynsbegäran mail.docx", "Gräsmyren")</f>
         <v/>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Sluttande myrmosaik? Måttligt påverkat av dikning?</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1870,6 +2164,43 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Floarna prioriterade fågelarter.docx", "Floarna")</f>
         <v/>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Ja, mindre i V</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Måste rekas noggrannt! Svårbedömt. Starkast i S troligen</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hög påverkan</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Stavakaraktär, ställvis gallrad
+Artfynd. Gammeltallar och silverved</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -2008,6 +2339,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Juånäset prioriterade fågelarter.docx", "Juånäset")</f>
         <v/>
       </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Helt avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Ser mycket bra ut</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Redan inventerat av Basti o Karolin</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -2146,6 +2513,43 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Fröbäckstjärnarna prioriterade fågelarter.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Ja, ett par ganska stor</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Enormt område, mycket svårbedömt, måste rekas noggrannt!!!</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Troligen hög</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Märrviksbodarna (Basti): Produktiva tallskogar, ofta genomgallrade
+Granskogsområden ser fina ut.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -2275,6 +2679,44 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Bodsjön prioriterade fågelarter.docx", "Bodsjön")</f>
         <v/>
       </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hela N halvan avv</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Hårt påverkat, men ser bra ut</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Hög påverkan</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Lst: skogen väster därom inventerades av lst 2004 och bedömdes som lägre naturvärden</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -2400,6 +2842,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Holmnäset tillsynsbegäran mail.docx", "Holmnäset")</f>
         <v/>
       </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Enorm avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Ser ut att vara stavatall</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Låg, kanske något gallrad</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Redan inventerat av Basti o Karolin</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -2527,6 +3005,40 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Staverberget SCA prioriterade fågelarter.docx", "Staverberget SCA")</f>
         <v/>
       </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Ja, stor avv centralt</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Ser bra ut! Gallrat i norr</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v/>
+      </c>
+      <c r="AL14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -2654,6 +3166,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Björnbäcken prioriterade fågelarter.docx", "Björnbäcken")</f>
         <v/>
       </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>SCA + privat i SV</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Ja, i N</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Ser bra ut, lövrik granskog?</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>a: Blndsumpskog, hänglavrik. Senvuxna granar och spridd död ved. Tretåig hackspett. Gammelskog. b: lövrik granskog ca 80-100år. Orörd, kolvedshuggning. Örtrik. Spridda gammalgranar</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -2775,6 +3323,44 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Börsåsen N tillsynsbegäran mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Avv i NV</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Svårbedömt. Ställvis gallrat, ställvis kontinuitetsbrutet? Kan vara fin stava också. Gränsar mot nya Hortesreservatet.</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Måttlig?</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>(sämre väg med högre vegetation)
+Produktiv, lövrik granskog.
+Stort aspinslag mkt död ved. Knärot, ögonpyrol, torta, Lunglav, korallblylav, vedtrappmossa</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -2894,6 +3480,43 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kilkojan prioriterade fågelarter.docx", "Kilkojan")</f>
         <v/>
       </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v/>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Ser bra ut!!!</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Sista biten av vägen S dålig, parkera en bit ner
+S: Ca 150-årig skog föryngrad efter brand. Få äldre tallar. Lövet utgånget? Allmänt med färsk ved, sparsamt med kelo. Rikt på garnlav.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -3014,6 +3637,44 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kölavallhöjden prioriterade fågelarter.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Ser mycket bra ut</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Lst: avsättning hos SCA</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -3130,6 +3791,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Trollkärringberget tillsynsbegäran mail.docx", "Trollkärringberget")</f>
         <v/>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>SCA + privat i SV</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Ja, i N</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v/>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Ser bra ut, lövrik granskog?</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>a: Blndsumpskog, hänglavrik. Senvuxna granar och spridd död ved. Tretåig hackspett. Gammelskog. b: lövrik granskog ca 80-100år. Orörd, kolvedshuggning. Örtrik. Spridda gammalgranar</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -3241,6 +3938,40 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Nils-Andersknulen N prioriterade fågelarter.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Flera avv</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v/>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Ser bra ut. Synd på vindkraftverken.</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -3353,6 +4084,40 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Blåtjärnen prioriterade fågelarter.docx", "Blåtjärnen")</f>
         <v/>
       </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v/>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Ser ut som fin stava</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -3456,6 +4221,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Sjättnäsbäcken SCA tillsynsbegäran mail.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v/>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Tycker det ser bra ut! Nära</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Halvbra, V3. Lövrik granskog.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -3562,6 +4363,42 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Rammsjöberget V Sveaskog tillsynsbegäran mail.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Sveaskog, Holmen</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Två avv-anm</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v/>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Ser inte jättebra ut, men ändå intressant bergssluttning</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Hårt påverkat</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Klockren NB i O. Reka nedan berget.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3627,6 +4464,45 @@
         <v>0</v>
       </c>
       <c r="U24" s="2" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Stor del av omr avsatt</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Delvis gallrat</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Sinnessjukt fint
+Urskogsartad stavatall blandat med gallrad stava. Skandal.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL24"/>
+  <dimension ref="A1:AL60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Horten Sultentjärnen</t>
+          <t>Halstjärnarna</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1312,22 +1312,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>175.9</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -1336,18 +1336,420 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>48</v>
+      </c>
+      <c r="R5" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" t="n">
+        <v>66</v>
+      </c>
+      <c r="T5" t="n">
+        <v>577</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Kolticka
+Kritporing
+Urskogsporing
+Doftticka
+Fläckporing
+Garnlav
+Goliatmusseron
+Gräddporing
+Gränsticka
+Knärot
+Laxgröppa
+Rostskinn
+Skrovlig taggsvamp
+Smalfotad taggsvamp
+Smultronkantarell
+Tajgataggsvamp
+Apelsinticka
+Blanksvart spiklav
+Blek lundlav
+Blå taggsvamp
+Blågrå svartspik
+Brunpudrad nållav
+Dropptaggsvamp
+Dvärgbägarlav
+Gammelgransskål
+Grå blåbärsfältmätare
+Knottrig blåslav
+Kolflarnlav
+Kortskaftad ärgspik
+Kådvaxskinn
+Lunglav
+Mörk kolflarnlav
+Nordtagging
+Orange taggsvamp
+Skarp dropptaggsvamp
+Skorpgelélav
+Skrovellav
+Talltagel
+Tallticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vaddporing
+Vedflamlav
+Vedskivlav
+Vedtrappmossa
+Vitgrynig nållav
+Vitplätt
+Bollvitmossa
+Bårdlav
+Flagellkvastmossa
+Grönpyrola
+Gytterlav
+Korallblylav
+Luddlav
+Norrlandslav
+Nästlav
+Skinnlav
+Spindelblomster
+Stuplav
+Vedticka
+Vågbandad barkbock
+Tjäder
+Fiskgjuse
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="V5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Halstjärnarna artfynd.xlsx", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Halstjärnarna karta.png", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Halstjärnarna georefererad karta.tif", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Halstjärnarna karta knärot.png", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Halstjärnarna FSC-klagomål.docx", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Halstjärnarna FSC-klagomål mail.docx", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Halstjärnarna tillsynsbegäran.docx", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Halstjärnarna tillsynsbegäran mail.docx", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Halstjärnarna prioriterade fågelarter.docx", "Halstjärnarna")</f>
+        <v/>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ser bra ut</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Stor påverkan centralt, annars ganska låg</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Staverberget - PRIVAT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" t="n">
+        <v>19</v>
+      </c>
+      <c r="L6" t="n">
+        <v>31</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>40</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9</v>
+      </c>
+      <c r="S6" t="n">
+        <v>66</v>
+      </c>
+      <c r="T6" t="n">
+        <v>668</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Kolticka
+Kritporing
+Doftticka
+Fläckporing
+Garnlav
+Gräddporing
+Gränsticka
+Knärot
+Ulltickeporing
+Blanksvart spiklav
+Blågrå svartspik
+Doftskinn
+Dropptaggsvamp
+Dvärgbägarlav
+Gammelgransskål
+Harticka
+Kandelabersvamp
+Knottrig blåslav
+Kolflarnlav
+Kortskaftad ärgspik
+Liten svartspik
+Lunglav
+Mörk kolflarnlav
+Nordtagging
+Rosenticka
+Skogsfru
+Skrovellav
+Skuggblåslav
+Stiftgelélav
+Stjärntagging
+Talltagel
+Tallticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedflamlav
+Vedskivlav
+Vedtrappmossa
+Violettgrå tagellav
+Vitgrynig nållav
+Bårdlav
+Grovticka
+Grönpyrola
+Gytterlav
+Korallblylav
+Korallrot
+Källpraktmossa
+Luddlav
+Mindre märgborre
+Norrlandslav
+Plattlummer
+Skinnlav
+Skogshakmossa
+Smal svampklubba
+Sotriska
+Spindelblomster
+Stuplav
+Tvåblad
+Vedticka
+Järpe
+Spillkråka
+Tjäder
+Svartvit flugsnappare
+Trana
+Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="V6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Staverberget - PRIVAT artfynd.xlsx", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Staverberget - PRIVAT karta.png", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Staverberget - PRIVAT georefererad karta.tif", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Staverberget - PRIVAT karta knärot.png", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Staverberget - PRIVAT FSC-klagomål.docx", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Staverberget - PRIVAT FSC-klagomål mail.docx", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Staverberget - PRIVAT tillsynsbegäran.docx", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Staverberget - PRIVAT tillsynsbegäran mail.docx", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Staverberget - PRIVAT prioriterade fågelarter.docx", "Staverberget - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Privat</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ser bra ut! Gissar stavatall</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Horten Sultentjärnen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L7" t="n">
+        <v>31</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>42</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R7" t="n">
         <v>11</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S7" t="n">
         <v>63</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>1217</v>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Kolticka
 Kritporing
@@ -1414,143 +1816,337 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="V5">
+      <c r="V7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Horten Sultentjärnen artfynd.xlsx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Horten Sultentjärnen karta.png", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Horten Sultentjärnen georefererad karta.tif", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Horten Sultentjärnen karta knärot.png", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Horten Sultentjärnen FSC-klagomål.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Horten Sultentjärnen FSC-klagomål mail.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Horten Sultentjärnen tillsynsbegäran.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Horten Sultentjärnen tillsynsbegäran mail.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Horten Sultentjärnen prioriterade fågelarter.docx", "Horten Sultentjärnen")</f>
         <v/>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Flera stora avv</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Delvis</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Ser riktigt bra ut!</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Låg</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK7" t="n">
         <v>1</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL7" t="n">
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Frägnhällorna O</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>200.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>33</v>
+      </c>
+      <c r="R8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S8" t="n">
+        <v>59</v>
+      </c>
+      <c r="T8" t="n">
+        <v>269</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp
+Aspfjädermossa
+Doftticka
+Garnlav
+Goliatmusseron
+Knärot
+Norsk näverlav
+Skrovlig taggsvamp
+Sprickporing
+Ulltickeporing
+Blå taggsvamp
+Brunpudrad nållav
+Doftskinn
+Dofttaggsvamp
+Dropptaggsvamp
+Dvärgbägarlav
+Gammelgransskål
+Kolflarnlav
+Lavskrika
+Lunglav
+Orange taggsvamp
+Rosenticka
+Rynkskinn
+Skrovellav
+Svartvit taggsvamp
+Talltaggsvamp
+Tallticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedflamlav
+Vedtrappmossa
+Violettgrå tagellav
+Bårdlav
+Fällmossa
+Gräsull
+Korallblylav
+Kransrams
+Luddlav
+Mörk husmossa
+Nordlig fjädermossa
+Plattlummer
+Rävticka
+Rödgul trumpetsvamp
+Skinnlav
+Spindelblomster
+Stor aspticka
+Strutbräken
+Stuplav
+Svart trolldruva
+Vedticka
+Zontaggsvamp
+Ögonpyrola
+Gråspett
+Spillkråka
+Tjäder
+Fläcknycklar
+Nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="V8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Frägnhällorna O artfynd.xlsx", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Frägnhällorna O karta.png", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Frägnhällorna O georefererad karta.tif", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Frägnhällorna O karta knärot.png", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Frägnhällorna O FSC-klagomål.docx", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Frägnhällorna O FSC-klagomål mail.docx", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Frägnhällorna O tillsynsbegäran.docx", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Frägnhällorna O tillsynsbegäran mail.docx", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Frägnhällorna O prioriterade fågelarter.docx", "Frägnhällorna O")</f>
+        <v/>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Stora Enso</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Ej avv</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Stora områden häll i S, prioritera norr om inv</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Måttlig</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Hundtjärnbrännan</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D9" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I9" t="n">
         <v>182.9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J9" t="n">
         <v>8</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K9" t="n">
         <v>12</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L9" t="n">
         <v>21</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N9" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>31</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R9" t="n">
         <v>10</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S9" t="n">
         <v>45</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T9" t="n">
         <v>249</v>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Urskogsticka
@@ -1599,143 +2195,143 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="V6">
+      <c r="V9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Hundtjärnbrännan artfynd.xlsx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="W6">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Hundtjärnbrännan karta.png", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Hundtjärnbrännan georefererad karta.tif", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Hundtjärnbrännan karta knärot.png", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Hundtjärnbrännan FSC-klagomål.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Hundtjärnbrännan FSC-klagomål mail.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Hundtjärnbrännan tillsynsbegäran.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Hundtjärnbrännan tillsynsbegäran mail.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Hundtjärnbrännan prioriterade fågelarter.docx", "Hundtjärnbrännan")</f>
         <v/>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>Stor avv i O</t>
         </is>
       </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>Mycket lovande, gränsar till två reservat</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>Troligen medelpåverkan</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK6" t="n">
+      <c r="AK9" t="n">
         <v>1</v>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>Lst Vst: Har rätt bra koll på detta omr</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Länken Vitalmen</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D10" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I10" t="n">
         <v>201</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K10" t="n">
         <v>12</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L10" t="n">
         <v>18</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M10" t="n">
         <v>6</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>24</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R10" t="n">
         <v>6</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S10" t="n">
         <v>41</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T10" t="n">
         <v>207</v>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Garnlav
@@ -1780,146 +2376,146 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V7">
+      <c r="V10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Länken Vitalmen artfynd.xlsx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Länken Vitalmen karta.png", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Länken Vitalmen georefererad karta.tif", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Länken Vitalmen karta knärot.png", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Länken Vitalmen FSC-klagomål.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Länken Vitalmen FSC-klagomål mail.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Länken Vitalmen tillsynsbegäran.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Länken Vitalmen tillsynsbegäran mail.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Länken Vitalmen prioriterade fågelarter.docx", "Länken Vitalmen")</f>
         <v/>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>SCA + kyrkan</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>Flera avv</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>Liten del av omr</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>Ser tätt och bra ut</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>Låg</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK7" t="n">
+      <c r="AK10" t="n">
         <v>1</v>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>I s: Stavatall, 80-100, inga överståndare. Gallrad en gång länge sedan. Sparsamt med död ved.
 I N klockrent. U/V3</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Gräsmyren</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D11" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I11" t="n">
         <v>226</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K11" t="n">
         <v>15</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L11" t="n">
         <v>18</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>22</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R11" t="n">
         <v>4</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S11" t="n">
         <v>39</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T11" t="n">
         <v>147</v>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Grantickeporing
@@ -1962,133 +2558,133 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="V8">
+      <c r="V11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Gräsmyren artfynd.xlsx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Gräsmyren karta.png", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Gräsmyren georefererad karta.tif", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Gräsmyren FSC-klagomål.docx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Gräsmyren FSC-klagomål mail.docx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Gräsmyren tillsynsbegäran.docx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Gräsmyren tillsynsbegäran mail.docx", "Gräsmyren")</f>
         <v/>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>Sluttande myrmosaik? Måttligt påverkat av dikning?</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>Måttlig påverkan</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK8" t="n">
+      <c r="AK11" t="n">
         <v>1</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL11" t="n">
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Floarna</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D12" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I12" t="n">
         <v>724.7</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L12" t="n">
         <v>22</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>30</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S12" t="n">
         <v>36</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T12" t="n">
         <v>139</v>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Doftticka
@@ -2128,144 +2724,144 @@
 Utter</t>
         </is>
       </c>
-      <c r="V9">
+      <c r="V12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Floarna artfynd.xlsx", "Floarna")</f>
         <v/>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Floarna karta.png", "Floarna")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Floarna georefererad karta.tif", "Floarna")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Floarna karta knärot.png", "Floarna")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Floarna FSC-klagomål.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Floarna FSC-klagomål mail.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Floarna tillsynsbegäran.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Floarna tillsynsbegäran mail.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Floarna prioriterade fågelarter.docx", "Floarna")</f>
         <v/>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>Ja, mindre i V</t>
         </is>
       </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>Måste rekas noggrannt! Svårbedömt. Starkast i S troligen</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>Hög påverkan</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK12" t="n">
         <v>1</v>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>Stavakaraktär, ställvis gallrad
 Artfynd. Gammeltallar och silverved</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Juånäset</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I13" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>15</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>7</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>18</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
         <v>3</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S13" t="n">
         <v>34</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T13" t="n">
         <v>109</v>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Storspov
 Garnlav
@@ -2303,143 +2899,143 @@
 Trana</t>
         </is>
       </c>
-      <c r="V10">
+      <c r="V13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Juånäset artfynd.xlsx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Juånäset karta.png", "Juånäset")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Juånäset georefererad karta.tif", "Juånäset")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Juånäset karta knärot.png", "Juånäset")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Juånäset FSC-klagomål.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Juånäset FSC-klagomål mail.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Juånäset tillsynsbegäran.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Juånäset tillsynsbegäran mail.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Juånäset prioriterade fågelarter.docx", "Juånäset")</f>
         <v/>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>Helt avverkningsanmält</t>
         </is>
       </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>Ser mycket bra ut</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>Låg påverkan</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK13" t="n">
         <v>1</v>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>Redan inventerat av Basti o Karolin</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D14" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I14" t="n">
         <v>751.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L14" t="n">
         <v>20</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M14" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>26</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R14" t="n">
         <v>6</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S14" t="n">
         <v>34</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T14" t="n">
         <v>240</v>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Fläckporing
@@ -2477,144 +3073,473 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V11">
+      <c r="V14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Fröbäckstjärnarna artfynd.xlsx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Fröbäckstjärnarna karta.png", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Fröbäckstjärnarna georefererad karta.tif", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Fröbäckstjärnarna karta knärot.png", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Fröbäckstjärnarna FSC-klagomål.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Fröbäckstjärnarna FSC-klagomål mail.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Fröbäckstjärnarna tillsynsbegäran.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Fröbäckstjärnarna tillsynsbegäran mail.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Fröbäckstjärnarna prioriterade fågelarter.docx", "Fröbäckstjärnarna")</f>
         <v/>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>Ja, ett par ganska stor</t>
         </is>
       </c>
-      <c r="AG11" t="n">
-        <v/>
-      </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>Enormt område, mycket svårbedömt, måste rekas noggrannt!!!</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>Troligen hög</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK14" t="n">
         <v>1</v>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>Märrviksbodarna (Basti): Produktiva tallskogar, ofta genomgallrade
 Granskogsområden ser fina ut.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Galvattsberget</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>19</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>31</v>
+      </c>
+      <c r="T15" t="n">
+        <v>133</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>Blackticka
+Doftticka
+Garnlav
+Knärot
+Doftskinn
+Dvärgbägarlav
+Gammelgransskål
+Harticka
+Kolflarnlav
+Lunglav
+Mörk kolflarnlav
+Rosenticka
+Rynkskinn
+Skrovellav
+Skrovlig flatbagge
+Tretåig hackspett
+Ullticka
+Vedskivlav
+Violettgrå tagellav
+Bronshjon
+Bårdlav
+Korallblylav
+Kransrams
+Luddlav
+Nästlav
+Skinnlav
+Spindelblomster
+Stuplav
+Trådticka
+Vedticka
+Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="V15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Galvattsberget artfynd.xlsx", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Galvattsberget karta.png", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Galvattsberget georefererad karta.tif", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Galvattsberget karta knärot.png", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Galvattsberget FSC-klagomål.docx", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Galvattsberget FSC-klagomål mail.docx", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Galvattsberget tillsynsbegäran.docx", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Galvattsberget tillsynsbegäran mail.docx", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Galvattsberget prioriterade fågelarter.docx", "Galvattsberget")</f>
+        <v/>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Brant! Fokusera på N och S. Ser bra ut!</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL15" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gärdsjögucken</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>20</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>28</v>
+      </c>
+      <c r="T16" t="n">
+        <v>193</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Gräddporing
+Knärot
+Blågrå svartspik
+Brunpudrad nållav
+Dropptaggsvamp
+Dvärgbägarlav
+Kolflarnlav
+Kortskaftad ärgspik
+Lunglav
+Mörk kolflarnlav
+Nordtagging
+Skrovellav
+Talltita
+Tretåig hackspett
+Ullticka
+Vedflamlav
+Vedskivlav
+Vedtrappmossa
+Violettgrå tagellav
+Barkkornlav
+Blodticka
+Korallblylav
+Norrlandslav
+Stuplav
+Vedticka
+Järpe
+Tjäder</t>
+        </is>
+      </c>
+      <c r="V16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Gärdsjögucken artfynd.xlsx", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Gärdsjögucken karta.png", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Gärdsjögucken georefererad karta.tif", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Gärdsjögucken karta knärot.png", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Gärdsjögucken FSC-klagomål.docx", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Gärdsjögucken FSC-klagomål mail.docx", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Gärdsjögucken tillsynsbegäran.docx", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Gärdsjögucken tillsynsbegäran mail.docx", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Gärdsjögucken prioriterade fågelarter.docx", "Gärdsjögucken")</f>
+        <v/>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Gissningsvis tät stavatall</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Bodsjön</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D17" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I17" t="n">
         <v>49.7</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J17" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K17" t="n">
         <v>7</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L17" t="n">
         <v>11</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>13</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S17" t="n">
         <v>25</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T17" t="n">
         <v>90</v>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2643,145 +3568,145 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V12">
+      <c r="V17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Bodsjön artfynd.xlsx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="W12">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Bodsjön karta.png", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Bodsjön georefererad karta.tif", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Bodsjön karta knärot.png", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Bodsjön FSC-klagomål.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Bodsjön FSC-klagomål mail.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Bodsjön tillsynsbegäran.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Bodsjön tillsynsbegäran mail.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Bodsjön prioriterade fågelarter.docx", "Bodsjön")</f>
         <v/>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>Hela N halvan avv</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>Delvis</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>Hårt påverkat, men ser bra ut</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>Hög påverkan</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK17" t="n">
         <v>1</v>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>Lst: skogen väster därom inventerades av lst 2004 och bedömdes som lägre naturvärden</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Holmnäset</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="D18" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I18" t="n">
         <v>163.9</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L18" t="n">
         <v>15</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M18" t="n">
         <v>4</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>20</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R18" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S18" t="n">
         <v>25</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T18" t="n">
         <v>141</v>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>Urskogsporing
 Fläckporing
@@ -2810,139 +3735,299 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V13">
+      <c r="V18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Holmnäset artfynd.xlsx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="W13">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Holmnäset karta.png", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Holmnäset georefererad karta.tif", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Holmnäset karta knärot.png", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Holmnäset FSC-klagomål.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Holmnäset FSC-klagomål mail.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Holmnäset tillsynsbegäran.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Holmnäset tillsynsbegäran mail.docx", "Holmnäset")</f>
         <v/>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>Enorm avverkningsanmälan</t>
         </is>
       </c>
-      <c r="AG13" t="n">
-        <v/>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AG18" t="n">
+        <v/>
+      </c>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>Ser ut att vara stavatall</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>Låg, kanske något gallrad</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK18" t="n">
         <v>1</v>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>Redan inventerat av Basti o Karolin</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rörmyrberget utökn N</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>232.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>17</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>85</v>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Garnlav
+Knärot
+Dvärgbägarlav
+Lunglav
+Mörk kolflarnlav
+Nordtagging
+Reliktbock
+Slät tallkapuschongbagge
+Stiftgelélav
+Tallticka
+Talltita
+Tretåig hackspett
+Ullticka
+Vedflamlav
+Vedtrappmossa
+Vitplätt
+Bollvitmossa
+Grönpyrola
+Korallblylav
+Norrlandslav
+Skinnlav
+Stuplav
+Orre
+Nattviol</t>
+        </is>
+      </c>
+      <c r="V19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Rörmyrberget utökn N artfynd.xlsx", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Rörmyrberget utökn N karta.png", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Rörmyrberget utökn N georefererad karta.tif", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Rörmyrberget utökn N karta knärot.png", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Rörmyrberget utökn N FSC-klagomål.docx", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Rörmyrberget utökn N FSC-klagomål mail.docx", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Rörmyrberget utökn N tillsynsbegäran.docx", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Rörmyrberget utökn N tillsynsbegäran mail.docx", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Rörmyrberget utökn N prioriterade fågelarter.docx", "Rörmyrberget utökn N")</f>
+        <v/>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Endast lite i V</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Ser ganska påverkat ut</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL19" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Staverberget SCA</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D20" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I20" t="n">
         <v>115.3</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J20" t="n">
         <v>7</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L20" t="n">
         <v>13</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M20" t="n">
         <v>4</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>17</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R20" t="n">
         <v>4</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S20" t="n">
         <v>23</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T20" t="n">
         <v>82</v>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Garnlav
@@ -2969,141 +4054,141 @@
 Orre</t>
         </is>
       </c>
-      <c r="V14">
+      <c r="V20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Staverberget SCA artfynd.xlsx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="W14">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Staverberget SCA karta.png", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Staverberget SCA georefererad karta.tif", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Staverberget SCA karta knärot.png", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Staverberget SCA FSC-klagomål.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Staverberget SCA FSC-klagomål mail.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Staverberget SCA tillsynsbegäran.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Staverberget SCA tillsynsbegäran mail.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Staverberget SCA prioriterade fågelarter.docx", "Staverberget SCA")</f>
         <v/>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>Ja, stor avv centralt</t>
         </is>
       </c>
-      <c r="AG14" t="n">
-        <v/>
-      </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AG20" t="n">
+        <v/>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>Ser bra ut! Gallrat i norr</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>Måttlig påverkan</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK14" t="n">
-        <v/>
-      </c>
-      <c r="AL14" t="n">
+      <c r="AK20" t="n">
+        <v/>
+      </c>
+      <c r="AL20" t="n">
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Björnbäcken</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D21" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I21" t="n">
         <v>61.4</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J21" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K21" t="n">
         <v>5</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L21" t="n">
         <v>12</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>15</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R21" t="n">
         <v>3</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S21" t="n">
         <v>23</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T21" t="n">
         <v>74</v>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
@@ -3130,143 +4215,300 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="V15">
+      <c r="V21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Björnbäcken artfynd.xlsx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="W15">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Björnbäcken karta.png", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Björnbäcken georefererad karta.tif", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Björnbäcken karta knärot.png", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Björnbäcken FSC-klagomål.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Björnbäcken FSC-klagomål mail.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Björnbäcken tillsynsbegäran.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Björnbäcken tillsynsbegäran mail.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Björnbäcken prioriterade fågelarter.docx", "Björnbäcken")</f>
         <v/>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>SCA + privat i SV</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>Ja, i N</t>
         </is>
       </c>
-      <c r="AG15" t="n">
-        <v/>
-      </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AG21" t="n">
+        <v/>
+      </c>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>Ser bra ut, lövrik granskog?</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>Låg</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK21" t="n">
         <v>1</v>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>a: Blndsumpskog, hänglavrik. Senvuxna granar och spridd död ved. Tretåig hackspett. Gammelskog. b: lövrik granskog ca 80-100år. Orörd, kolvedshuggning. Örtrik. Spridda gammalgranar</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gucken</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>44</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>17</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>22</v>
+      </c>
+      <c r="T22" t="n">
+        <v>60</v>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>Doftticka
+Fläckporing
+Garnlav
+Knärot
+Liten aspgelélav
+Doftskinn
+Harticka
+Kungsörn
+Lunglav
+Rosenticka
+Skrovellav
+Stiftgelélav
+Talltita
+Tretåig hackspett
+Ullticka
+Vedtrappmossa
+Vitgrynig nållav
+Korallblylav
+Skinnlav
+Stuplav
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="V22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Gucken artfynd.xlsx", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Gucken karta.png", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Gucken georefererad karta.tif", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Gucken karta knärot.png", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Gucken FSC-klagomål.docx", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Gucken FSC-klagomål mail.docx", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Gucken tillsynsbegäran.docx", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Gucken tillsynsbegäran mail.docx", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Gucken prioriterade fågelarter.docx", "Gucken")</f>
+        <v/>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Ganska påverkat. Brant.</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Hög påverkan</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL22" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Börsåsen N</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D23" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I23" t="n">
         <v>124.6</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J23" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K23" t="n">
         <v>8</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L23" t="n">
         <v>9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M23" t="n">
         <v>3</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>12</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R23" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S23" t="n">
         <v>21</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T23" t="n">
         <v>63</v>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Garnlav
@@ -3291,70 +4533,70 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="V16">
+      <c r="V23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Börsåsen N artfynd.xlsx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="W16">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Börsåsen N karta.png", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Börsåsen N georefererad karta.tif", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Börsåsen N karta knärot.png", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Börsåsen N FSC-klagomål.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Börsåsen N FSC-klagomål mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Börsåsen N tillsynsbegäran.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Börsåsen N tillsynsbegäran mail.docx", "Börsåsen N")</f>
         <v/>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>Avv i NV</t>
         </is>
       </c>
-      <c r="AG16" t="n">
-        <v/>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AG23" t="n">
+        <v/>
+      </c>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>Svårbedömt. Ställvis gallrat, ställvis kontinuitetsbrutet? Kan vara fin stava också. Gränsar mot nya Hortesreservatet.</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>Måttlig?</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK23" t="n">
         <v>1</v>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>(sämre väg med högre vegetation)
 Produktiv, lövrik granskog.
@@ -3362,70 +4604,70 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Kilkojan</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="D24" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I24" t="n">
         <v>162.6</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>15</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M24" t="n">
         <v>4</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>19</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R24" t="n">
         <v>4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S24" t="n">
         <v>19</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T24" t="n">
         <v>56</v>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Fläckporing
@@ -3448,140 +4690,440 @@
 Vitplätt</t>
         </is>
       </c>
-      <c r="V17">
+      <c r="V24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Kilkojan artfynd.xlsx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="W17">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Kilkojan karta.png", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Kilkojan georefererad karta.tif", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="Z24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Kilkojan FSC-klagomål.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Kilkojan FSC-klagomål mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Kilkojan tillsynsbegäran.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Kilkojan tillsynsbegäran mail.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kilkojan prioriterade fågelarter.docx", "Kilkojan")</f>
         <v/>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="AG17" t="n">
-        <v/>
-      </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AG24" t="n">
+        <v/>
+      </c>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>Ser bra ut!!!</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>Låg påverkan</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK24" t="n">
         <v>1</v>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>Sista biten av vägen S dålig, parkera en bit ner
 S: Ca 150-årig skog föryngrad efter brand. Få äldre tallar. Lövet utgånget? Allmänt med färsk ved, sparsamt med kelo. Rikt på garnlav.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lövbergsgraven</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>17</v>
+      </c>
+      <c r="T25" t="n">
+        <v>39</v>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Kolflarnlav
+Lunglav
+Skrovellav
+Skuggblåslav
+Vedskivlav
+Vedtrappmossa
+Vitgrynig nållav
+Bårdlav
+Korallblylav
+Korallrot
+Luddlav
+Skinnlav
+Spindelblomster
+Fläcknycklar
+Nattviol</t>
+        </is>
+      </c>
+      <c r="V25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Lövbergsgraven artfynd.xlsx", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Lövbergsgraven karta.png", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Lövbergsgraven georefererad karta.tif", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Lövbergsgraven karta knärot.png", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Lövbergsgraven FSC-klagomål.docx", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Lövbergsgraven FSC-klagomål mail.docx", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Lövbergsgraven tillsynsbegäran.docx", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Lövbergsgraven tillsynsbegäran mail.docx", "Lövbergsgraven")</f>
+        <v/>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Stora Enso</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Ser ok ut</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Måttligt påverkat</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL25" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ömansholmen</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>13</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>17</v>
+      </c>
+      <c r="T26" t="n">
+        <v>181</v>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Dropptaggsvamp
+Dvärgbägarlav
+Gammelgransskål
+Kolflarnlav
+Kortskaftad ärgspik
+Mörk kolflarnlav
+Reliktbock
+Tallticka
+Talltita
+Ullticka
+Vedskivlav
+Vedtrappmossa
+Norrlandslav
+Vedticka
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="V26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Ömansholmen artfynd.xlsx", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Ömansholmen karta.png", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Ömansholmen georefererad karta.tif", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Ömansholmen karta knärot.png", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Ömansholmen FSC-klagomål.docx", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Ömansholmen FSC-klagomål mail.docx", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Ömansholmen tillsynsbegäran.docx", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Ömansholmen tillsynsbegäran mail.docx", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Ömansholmen prioriterade fågelarter.docx", "Ömansholmen")</f>
+        <v/>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Ser ut som dödismorän. Påverkat men ser hett ut!</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL26" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Kölavallhöjden</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D27" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I27" t="n">
         <v>57.8</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J27" t="n">
         <v>3</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K27" t="n">
         <v>5</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L27" t="n">
         <v>8</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M27" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>10</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R27" t="n">
         <v>2</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S27" t="n">
         <v>16</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T27" t="n">
         <v>36</v>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Knärot
@@ -3601,145 +5143,145 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="V18">
+      <c r="V27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Kölavallhöjden artfynd.xlsx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="W18">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Kölavallhöjden karta.png", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Kölavallhöjden georefererad karta.tif", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Kölavallhöjden karta knärot.png", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Kölavallhöjden FSC-klagomål.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Kölavallhöjden FSC-klagomål mail.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Kölavallhöjden tillsynsbegäran.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Kölavallhöjden tillsynsbegäran mail.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Kölavallhöjden prioriterade fågelarter.docx", "Kölavallhöjden")</f>
         <v/>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>Ser mycket bra ut</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>Låg påverkan</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK27" t="n">
         <v>1</v>
       </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AL27" t="inlineStr">
         <is>
           <t>Lst: avsättning hos SCA</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Trollkärringberget</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D28" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I28" t="n">
         <v>18.8</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K28" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L28" t="n">
         <v>6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M28" t="n">
         <v>3</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>9</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R28" t="n">
         <v>3</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S28" t="n">
         <v>16</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T28" t="n">
         <v>39</v>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -3759,139 +5301,575 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="V19">
+      <c r="V28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Trollkärringberget artfynd.xlsx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="W19">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Trollkärringberget karta.png", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Trollkärringberget georefererad karta.tif", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Trollkärringberget karta knärot.png", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Trollkärringberget FSC-klagomål.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Trollkärringberget FSC-klagomål mail.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Trollkärringberget tillsynsbegäran.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Trollkärringberget tillsynsbegäran mail.docx", "Trollkärringberget")</f>
         <v/>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>SCA + privat i SV</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>Ja, i N</t>
         </is>
       </c>
-      <c r="AG19" t="n">
-        <v/>
-      </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AG28" t="n">
+        <v/>
+      </c>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>Ser bra ut, lövrik granskog?</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>Låg</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK28" t="n">
         <v>1</v>
       </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>a: Blndsumpskog, hänglavrik. Senvuxna granar och spridd död ved. Tretåig hackspett. Gammelskog. b: lövrik granskog ca 80-100år. Orörd, kolvedshuggning. Örtrik. Spridda gammalgranar</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norrbodstugan</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="n">
+        <v>49</v>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Harticka
+Lavskrika
+Lunglav
+Skrovellav
+Talltita
+Tretåig hackspett
+Ullticka
+Luddlav
+Spindelblomster
+Stuplav
+Trådticka
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="V29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Norrbodstugan artfynd.xlsx", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Norrbodstugan karta.png", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Norrbodstugan georefererad karta.tif", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Norrbodstugan karta knärot.png", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Norrbodstugan FSC-klagomål.docx", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Norrbodstugan FSC-klagomål mail.docx", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Norrbodstugan tillsynsbegäran.docx", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Norrbodstugan tillsynsbegäran mail.docx", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Norrbodstugan prioriterade fågelarter.docx", "Norrbodstugan")</f>
+        <v/>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Flera mindre avv</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Ser helt ok ut</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Måttlig till hög</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL29" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hedberget</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>14</v>
+      </c>
+      <c r="T30" t="n">
+        <v>47</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>Doftticka
+Fjällig taggsvamp s.str.
+Järnsparv
+Lunglav
+Skrovellav
+Bårdlav
+Korallblylav
+Skinnlav
+Stor aspticka
+Stuplav
+Svavelriska
+Järpe
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="V30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Hedberget artfynd.xlsx", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Hedberget karta.png", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Hedberget georefererad karta.tif", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Hedberget FSC-klagomål.docx", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Hedberget FSC-klagomål mail.docx", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Hedberget tillsynsbegäran.docx", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Hedberget tillsynsbegäran mail.docx", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Hedberget prioriterade fågelarter.docx", "Hedberget")</f>
+        <v/>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Kan vara ok</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL30" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rödhusberget - SCA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>12</v>
+      </c>
+      <c r="T31" t="n">
+        <v>29</v>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Gräddporing
+Lateritticka
+Blanksvart spiklav
+Dvärgbägarlav
+Knottrig blåslav
+Kolflarnlav
+Kortskaftad ärgspik
+Lunglav
+Reliktbock
+Vedflamlav
+Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="V31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Rödhusberget - SCA artfynd.xlsx", "Rödhusberget - SCA")</f>
+        <v/>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Rödhusberget - SCA karta.png", "Rödhusberget - SCA")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Rödhusberget - SCA georefererad karta.tif", "Rödhusberget - SCA")</f>
+        <v/>
+      </c>
+      <c r="Z31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Rödhusberget - SCA FSC-klagomål.docx", "Rödhusberget - SCA")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Rödhusberget - SCA FSC-klagomål mail.docx", "Rödhusberget - SCA")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Rödhusberget - SCA tillsynsbegäran.docx", "Rödhusberget - SCA")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Rödhusberget - SCA tillsynsbegäran mail.docx", "Rödhusberget - SCA")</f>
+        <v/>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Ser ok ut! Inslag av NB</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Bör rekas i norr. Utställt, få överståndare, dåligt med ved i S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Nils-Andersknulen N</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="D32" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I32" t="n">
         <v>45.3</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K32" t="n">
         <v>3</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L32" t="n">
         <v>6</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>8</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R32" t="n">
         <v>2</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S32" t="n">
         <v>11</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T32" t="n">
         <v>12</v>
       </c>
-      <c r="U20" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>Blackticka
 Gränsticka
@@ -3906,137 +5884,419 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="V20">
+      <c r="V32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Nils-Andersknulen N artfynd.xlsx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="W20">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Nils-Andersknulen N karta.png", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Nils-Andersknulen N georefererad karta.tif", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="Z32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Nils-Andersknulen N FSC-klagomål.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Nils-Andersknulen N FSC-klagomål mail.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Nils-Andersknulen N tillsynsbegäran.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Nils-Andersknulen N tillsynsbegäran mail.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Nils-Andersknulen N prioriterade fågelarter.docx", "Nils-Andersknulen N")</f>
         <v/>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>Flera avv</t>
         </is>
       </c>
-      <c r="AG20" t="n">
-        <v/>
-      </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AG32" t="n">
+        <v/>
+      </c>
+      <c r="AH32" t="inlineStr">
         <is>
           <t>Ser bra ut. Synd på vindkraftverken.</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>Låg påverkan</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK20" t="n">
+      <c r="AK32" t="n">
         <v>1</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AL32" t="n">
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Långsidberget V</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>10</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="n">
+        <v>10</v>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Gräddporing
+Knärot
+Smalfotad taggsvamp
+Dropptaggsvamp
+Dvärgbägarlav
+Kungsörn
+Motaggsvamp
+Nordtagging
+Vaddporing</t>
+        </is>
+      </c>
+      <c r="V33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Långsidberget V artfynd.xlsx", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Långsidberget V karta.png", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Långsidberget V georefererad karta.tif", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Långsidberget V karta knärot.png", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="Z33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Långsidberget V FSC-klagomål.docx", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Långsidberget V FSC-klagomål mail.docx", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Långsidberget V tillsynsbegäran.docx", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Långsidberget V tillsynsbegäran mail.docx", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Långsidberget V prioriterade fågelarter.docx", "Långsidberget V")</f>
+        <v/>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Hela avv-anm</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Sägs vara mycket fin skog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Låg/måttlig</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL33" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sandnäsgrottan</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>10</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="n">
+        <v>16</v>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>Blackticka
+Gränsticka
+Ulltickeporing
+Lunglav
+Rosenticka
+Skrovellav
+Stjärntagging
+Tallticka
+Ullticka
+Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="V34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Sandnäsgrottan artfynd.xlsx", "Sandnäsgrottan")</f>
+        <v/>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Sandnäsgrottan karta.png", "Sandnäsgrottan")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Sandnäsgrottan georefererad karta.tif", "Sandnäsgrottan")</f>
+        <v/>
+      </c>
+      <c r="Z34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Sandnäsgrottan FSC-klagomål.docx", "Sandnäsgrottan")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Sandnäsgrottan FSC-klagomål mail.docx", "Sandnäsgrottan")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Sandnäsgrottan tillsynsbegäran.docx", "Sandnäsgrottan")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Sandnäsgrottan tillsynsbegäran mail.docx", "Sandnäsgrottan")</f>
+        <v/>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Ser ganska bra ut! Granskog?</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Blåtjärnen</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="D35" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I35" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>5</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S35" t="n">
         <v>8</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T35" t="n">
         <v>18</v>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dvärgbägarlav
@@ -4048,141 +6308,141 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="V21">
+      <c r="V35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Blåtjärnen artfynd.xlsx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="W21">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Blåtjärnen karta.png", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Blåtjärnen georefererad karta.tif", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Blåtjärnen karta knärot.png", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="Z35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Blåtjärnen FSC-klagomål.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Blåtjärnen FSC-klagomål mail.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Blåtjärnen tillsynsbegäran.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Blåtjärnen tillsynsbegäran mail.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Blåtjärnen prioriterade fågelarter.docx", "Blåtjärnen")</f>
         <v/>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="AG21" t="n">
-        <v/>
-      </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AG35" t="n">
+        <v/>
+      </c>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>Ser ut som fin stava</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Låg</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK21" t="n">
+      <c r="AK35" t="n">
         <v>1</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AL35" t="n">
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Sjättnäsbäcken SCA</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="D36" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I36" t="n">
         <v>35.4</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K36" t="n">
         <v>3</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R36" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S36" t="n">
         <v>7</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T36" t="n">
         <v>8</v>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lunglav
@@ -4193,135 +6453,135 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="V22">
+      <c r="V36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Sjättnäsbäcken SCA artfynd.xlsx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="W22">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Sjättnäsbäcken SCA karta.png", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Sjättnäsbäcken SCA georefererad karta.tif", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Sjättnäsbäcken SCA FSC-klagomål.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Sjättnäsbäcken SCA FSC-klagomål mail.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Sjättnäsbäcken SCA tillsynsbegäran.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Sjättnäsbäcken SCA tillsynsbegäran mail.docx", "Sjättnäsbäcken SCA")</f>
         <v/>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="AG22" t="n">
-        <v/>
-      </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AG36" t="n">
+        <v/>
+      </c>
+      <c r="AH36" t="inlineStr">
         <is>
           <t>Tycker det ser bra ut! Nära</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>Låg</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK22" t="n">
+      <c r="AK36" t="n">
         <v>1</v>
       </c>
-      <c r="AL22" t="inlineStr">
+      <c r="AL36" t="inlineStr">
         <is>
           <t>Halvbra, V3. Lövrik granskog.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Rammsjöberget V Sveaskog</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="D37" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I37" t="n">
         <v>81.2</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L37" t="n">
         <v>3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M37" t="n">
         <v>2</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>5</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R37" t="n">
         <v>2</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S37" t="n">
         <v>6</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T37" t="n">
         <v>10</v>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -4331,176 +6591,2818 @@
 Blodticka</t>
         </is>
       </c>
-      <c r="V23">
+      <c r="V37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Rammsjöberget V Sveaskog artfynd.xlsx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="W23">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Rammsjöberget V Sveaskog karta.png", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Rammsjöberget V Sveaskog georefererad karta.tif", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Rammsjöberget V Sveaskog karta knärot.png", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="Z37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Rammsjöberget V Sveaskog FSC-klagomål.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Rammsjöberget V Sveaskog FSC-klagomål mail.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Rammsjöberget V Sveaskog tillsynsbegäran.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Rammsjöberget V Sveaskog tillsynsbegäran mail.docx", "Rammsjöberget V Sveaskog")</f>
         <v/>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>Sveaskog, Holmen</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>Två avv-anm</t>
         </is>
       </c>
-      <c r="AG23" t="n">
-        <v/>
-      </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AG37" t="n">
+        <v/>
+      </c>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>Ser inte jättebra ut, men ändå intressant bergssluttning</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>Hårt påverkat</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK23" t="n">
+      <c r="AK37" t="n">
         <v>1</v>
       </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>Klockren NB i O. Reka nedan berget.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Köljesjön</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="n">
+        <v>9</v>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Dropptaggsvamp
+Kolflarnlav
+Lunglav
+Vedskivlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="V38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Köljesjön artfynd.xlsx", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="W38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Köljesjön karta.png", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Köljesjön georefererad karta.tif", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="Z38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Köljesjön FSC-klagomål.docx", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Köljesjön FSC-klagomål mail.docx", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Köljesjön tillsynsbegäran.docx", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Köljesjön tillsynsbegäran mail.docx", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Köljesjön prioriterade fågelarter.docx", "Köljesjön")</f>
+        <v/>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Ja, centralt</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Ser inte jättebra ut, men kan vara ok</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL38" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Börsåsen - PRIVAT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot
+Ögonpyrola
+Blåsippa
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="V39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Börsåsen - PRIVAT artfynd.xlsx", "Börsåsen - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Börsåsen - PRIVAT karta.png", "Börsåsen - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Börsåsen - PRIVAT georefererad karta.tif", "Börsåsen - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="Z39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Börsåsen - PRIVAT FSC-klagomål.docx", "Börsåsen - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Börsåsen - PRIVAT FSC-klagomål mail.docx", "Börsåsen - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Börsåsen - PRIVAT tillsynsbegäran.docx", "Börsåsen - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Börsåsen - PRIVAT tillsynsbegäran mail.docx", "Börsåsen - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Privat</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Ser ok ut</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL39" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lill-Börsåsen</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Blå taggsvamp
+Dropptaggsvamp
+Lunglav</t>
+        </is>
+      </c>
+      <c r="V40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Lill-Börsåsen artfynd.xlsx", "Lill-Börsåsen")</f>
+        <v/>
+      </c>
+      <c r="W40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Lill-Börsåsen karta.png", "Lill-Börsåsen")</f>
+        <v/>
+      </c>
+      <c r="X40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Lill-Börsåsen georefererad karta.tif", "Lill-Börsåsen")</f>
+        <v/>
+      </c>
+      <c r="Z40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Lill-Börsåsen FSC-klagomål.docx", "Lill-Börsåsen")</f>
+        <v/>
+      </c>
+      <c r="AA40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Lill-Börsåsen FSC-klagomål mail.docx", "Lill-Börsåsen")</f>
+        <v/>
+      </c>
+      <c r="AB40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Lill-Börsåsen tillsynsbegäran.docx", "Lill-Börsåsen")</f>
+        <v/>
+      </c>
+      <c r="AC40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Lill-Börsåsen tillsynsbegäran mail.docx", "Lill-Börsåsen")</f>
+        <v/>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>SCA i V, privat i O</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Svårbedömt, privat också...</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Måttligt påverkat</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL40" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Krogsand</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>7</v>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Lunglav
+Reliktbock
+Stuplav</t>
+        </is>
+      </c>
+      <c r="V41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Krogsand artfynd.xlsx", "Krogsand")</f>
+        <v/>
+      </c>
+      <c r="W41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Krogsand karta.png", "Krogsand")</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Krogsand georefererad karta.tif", "Krogsand")</f>
+        <v/>
+      </c>
+      <c r="Z41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Krogsand FSC-klagomål.docx", "Krogsand")</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Krogsand FSC-klagomål mail.docx", "Krogsand")</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Krogsand tillsynsbegäran.docx", "Krogsand")</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Krogsand tillsynsbegäran mail.docx", "Krogsand")</f>
+        <v/>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Helt avvanm</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Ser inte särskilt bra ut</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Hög påverkan</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL41" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gyllene druvan</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Doftskinn
+Lunglav
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="V42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Gyllene druvan artfynd.xlsx", "Gyllene druvan")</f>
+        <v/>
+      </c>
+      <c r="W42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Gyllene druvan karta.png", "Gyllene druvan")</f>
+        <v/>
+      </c>
+      <c r="X42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Gyllene druvan georefererad karta.tif", "Gyllene druvan")</f>
+        <v/>
+      </c>
+      <c r="Z42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Gyllene druvan FSC-klagomål.docx", "Gyllene druvan")</f>
+        <v/>
+      </c>
+      <c r="AA42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Gyllene druvan FSC-klagomål mail.docx", "Gyllene druvan")</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Gyllene druvan tillsynsbegäran.docx", "Gyllene druvan")</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Gyllene druvan tillsynsbegäran mail.docx", "Gyllene druvan")</f>
+        <v/>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Ser bra ut! Gissar granskog med asp</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Lövrik granskog ca 100-årig m sparsamt inslag av äldre. Underröjd.
+V3 - ej högsta prio</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Röjans sandtallskog</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>26</v>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>Fläckporing
+Gräddporing
+Dvärgbägarlav
+Reliktbock</t>
+        </is>
+      </c>
+      <c r="V43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Röjans sandtallskog artfynd.xlsx", "Röjans sandtallskog")</f>
+        <v/>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Röjans sandtallskog karta.png", "Röjans sandtallskog")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Röjans sandtallskog georefererad karta.tif", "Röjans sandtallskog")</f>
+        <v/>
+      </c>
+      <c r="Z43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Röjans sandtallskog FSC-klagomål.docx", "Röjans sandtallskog")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Röjans sandtallskog FSC-klagomål mail.docx", "Röjans sandtallskog")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Röjans sandtallskog tillsynsbegäran.docx", "Röjans sandtallskog")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Röjans sandtallskog tillsynsbegäran mail.docx", "Röjans sandtallskog")</f>
+        <v/>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Ser ut som potent marksvampslokal</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Hög påverkan</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL43" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Fagflobäcken - PRIVAT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>95</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Skarp dropptaggsvamp
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="V44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Fagflobäcken - PRIVAT artfynd.xlsx", "Fagflobäcken - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="W44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Fagflobäcken - PRIVAT karta.png", "Fagflobäcken - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Fagflobäcken - PRIVAT georefererad karta.tif", "Fagflobäcken - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="Z44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Fagflobäcken - PRIVAT FSC-klagomål.docx", "Fagflobäcken - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Fagflobäcken - PRIVAT FSC-klagomål mail.docx", "Fagflobäcken - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Fagflobäcken - PRIVAT tillsynsbegäran.docx", "Fagflobäcken - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Fagflobäcken - PRIVAT tillsynsbegäran mail.docx", "Fagflobäcken - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Privat</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Ser ganska bra ut! Gränsar mot blivande Hortesån-reservatet</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL44" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Fligget</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Tretåig hackspett
+Skinnlav</t>
+        </is>
+      </c>
+      <c r="V45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Fligget artfynd.xlsx", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Fligget karta.png", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Fligget georefererad karta.tif", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="Z45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Fligget FSC-klagomål.docx", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Fligget FSC-klagomål mail.docx", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Fligget tillsynsbegäran.docx", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Fligget tillsynsbegäran mail.docx", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Fligget prioriterade fågelarter.docx", "Fligget")</f>
+        <v/>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Litet, men ser mycket bra ut</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Låg</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL45" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sjättnäsbäcken Holmen</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="V46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Sjättnäsbäcken Holmen artfynd.xlsx", "Sjättnäsbäcken Holmen")</f>
+        <v/>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Sjättnäsbäcken Holmen karta.png", "Sjättnäsbäcken Holmen")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Sjättnäsbäcken Holmen georefererad karta.tif", "Sjättnäsbäcken Holmen")</f>
+        <v/>
+      </c>
+      <c r="Z46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Sjättnäsbäcken Holmen FSC-klagomål.docx", "Sjättnäsbäcken Holmen")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Sjättnäsbäcken Holmen FSC-klagomål mail.docx", "Sjättnäsbäcken Holmen")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Sjättnäsbäcken Holmen tillsynsbegäran.docx", "Sjättnäsbäcken Holmen")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Sjättnäsbäcken Holmen tillsynsbegäran mail.docx", "Sjättnäsbäcken Holmen")</f>
+        <v/>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Helt avv</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Ser inte så bra ut. Oklar kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL46" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Rammsjöberget S - PRIVAT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>Doftticka
+Korallblylav</t>
+        </is>
+      </c>
+      <c r="V47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Rammsjöberget S - PRIVAT artfynd.xlsx", "Rammsjöberget S - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Rammsjöberget S - PRIVAT karta.png", "Rammsjöberget S - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Rammsjöberget S - PRIVAT georefererad karta.tif", "Rammsjöberget S - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="Z47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Rammsjöberget S - PRIVAT FSC-klagomål.docx", "Rammsjöberget S - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Rammsjöberget S - PRIVAT FSC-klagomål mail.docx", "Rammsjöberget S - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Rammsjöberget S - PRIVAT tillsynsbegäran.docx", "Rammsjöberget S - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Rammsjöberget S - PRIVAT tillsynsbegäran mail.docx", "Rammsjöberget S - PRIVAT")</f>
+        <v/>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Privat</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Ja, ett par mindre</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Ganska varierat, svårbedömt, kan vara ok</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL47" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Skärsundnäsberget</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Duvhök</t>
+        </is>
+      </c>
+      <c r="V48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Skärsundnäsberget artfynd.xlsx", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="W48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Skärsundnäsberget karta.png", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Skärsundnäsberget georefererad karta.tif", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="Y48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/knärot/Skärsundnäsberget karta knärot.png", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="Z48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Skärsundnäsberget FSC-klagomål.docx", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Skärsundnäsberget FSC-klagomål mail.docx", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Skärsundnäsberget tillsynsbegäran.docx", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Skärsundnäsberget tillsynsbegäran mail.docx", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/fåglar/Skärsundnäsberget prioriterade fågelarter.docx", "Skärsundnäsberget")</f>
+        <v/>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Ser bra ut, om än ganska påverkat</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL48" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Furuberget</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Rosenticka</t>
+        </is>
+      </c>
+      <c r="V49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Furuberget artfynd.xlsx", "Furuberget")</f>
+        <v/>
+      </c>
+      <c r="W49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Furuberget karta.png", "Furuberget")</f>
+        <v/>
+      </c>
+      <c r="X49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Furuberget georefererad karta.tif", "Furuberget")</f>
+        <v/>
+      </c>
+      <c r="Z49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Furuberget FSC-klagomål.docx", "Furuberget")</f>
+        <v/>
+      </c>
+      <c r="AA49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Furuberget FSC-klagomål mail.docx", "Furuberget")</f>
+        <v/>
+      </c>
+      <c r="AB49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Furuberget tillsynsbegäran.docx", "Furuberget")</f>
+        <v/>
+      </c>
+      <c r="AC49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Furuberget tillsynsbegäran mail.docx", "Furuberget")</f>
+        <v/>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Sveaskog, Holmen</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Nästan helt avv-anm</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Gissningsvis halvbra barrblandskog</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Tämligen hårt påverkad</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL49" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hoan</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="V50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Hoan artfynd.xlsx", "Hoan")</f>
+        <v/>
+      </c>
+      <c r="W50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Hoan karta.png", "Hoan")</f>
+        <v/>
+      </c>
+      <c r="X50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Hoan georefererad karta.tif", "Hoan")</f>
+        <v/>
+      </c>
+      <c r="Z50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Hoan FSC-klagomål.docx", "Hoan")</f>
+        <v/>
+      </c>
+      <c r="AA50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Hoan FSC-klagomål mail.docx", "Hoan")</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Hoan tillsynsbegäran.docx", "Hoan")</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Hoan tillsynsbegäran mail.docx", "Hoan")</f>
+        <v/>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Bergvik?</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Svårbedömt. Kan vara kasst.</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Hög påverkan</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL50" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ruggelberget</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>239.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="V51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Ruggelberget artfynd.xlsx", "Ruggelberget")</f>
+        <v/>
+      </c>
+      <c r="W51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Ruggelberget karta.png", "Ruggelberget")</f>
+        <v/>
+      </c>
+      <c r="X51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Ruggelberget georefererad karta.tif", "Ruggelberget")</f>
+        <v/>
+      </c>
+      <c r="Z51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Ruggelberget FSC-klagomål.docx", "Ruggelberget")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Ruggelberget FSC-klagomål mail.docx", "Ruggelberget")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Ruggelberget tillsynsbegäran.docx", "Ruggelberget")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Ruggelberget tillsynsbegäran mail.docx", "Ruggelberget")</f>
+        <v/>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Stora Enso, privat</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Ser ganska bra ut. Dålig form.</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL51" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fågelmyrarna</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="V52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/artfynd/Fågelmyrarna artfynd.xlsx", "Fågelmyrarna")</f>
+        <v/>
+      </c>
+      <c r="W52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor/Fågelmyrarna karta.png", "Fågelmyrarna")</f>
+        <v/>
+      </c>
+      <c r="X52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/kartor_geotiff/Fågelmyrarna georefererad karta.tif", "Fågelmyrarna")</f>
+        <v/>
+      </c>
+      <c r="Z52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomål/Fågelmyrarna FSC-klagomål.docx", "Fågelmyrarna")</f>
+        <v/>
+      </c>
+      <c r="AA52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/klagomålsmail/Fågelmyrarna FSC-klagomål mail.docx", "Fågelmyrarna")</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsyn/Fågelmyrarna tillsynsbegäran.docx", "Fågelmyrarna")</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_FORSKNINGSRESAN_2023/tillsynsmail/Fågelmyrarna tillsynsbegäran mail.docx", "Fågelmyrarna")</f>
+        <v/>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Ser bra ut. Häll centralt .Bäck i O.</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL52" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Horten NV</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46222</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="D53" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Jämtlands län</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Berg</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I53" t="n">
         <v>86.2</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="2" t="inlineStr"/>
-      <c r="AE24" t="inlineStr">
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="AE53" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>Stor del av omr avsatt</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AH53" t="inlineStr">
         <is>
           <t>Delvis gallrat</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI53" t="inlineStr">
         <is>
           <t>Hög</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="AK24" t="n">
+      <c r="AK53" t="n">
         <v>1</v>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>Sinnessjukt fint
 Urskogsartad stavatall blandat med gallrad stava. Skandal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Långsidberget NO</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Nästan helt avv</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Ser ut som äldre gallrad tallskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Måttlig</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL54" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Skarpnäset</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Helt avv</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Kan nog vara ok</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Måttlig</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL55" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Getåsen C</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>SCA, lite privat</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Måste rekas noggrannt! Kan vara ogallrad stavatallskog, svårbedömt</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Svårbedömd</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL56" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Björnmyrbäcken</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>118</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Något varierande, men ser ut att hålla ihop bra</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Tydlig, äldre plock, sentida gallring, dikning</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL57" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Viberget N</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Ser bra ut, stor andel NB</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Låg påverkan</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL58" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Getåsen S</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Stora avv-anm över hela</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Ser inte bra ut</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Hög påverkan</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL59" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Forsensbrännan</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Jämtlands län</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Sandtallskog, ser bra ut!</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Måttlig påverkan</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Helt ok sandtallskog, inget mer
+V3</t>
         </is>
       </c>
     </row>
